--- a/public/template-faqs.xlsx
+++ b/public/template-faqs.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75041EF9-B49C-43D1-A4DD-6E49F4A36ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16392" windowHeight="6036"/>
+    <workbookView xWindow="-25125" yWindow="4635" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
   <si>
     <t>Intent</t>
   </si>
@@ -23,12 +24,48 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>greeting</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>helloday</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>operational</t>
+  </si>
+  <si>
+    <t>menu</t>
+  </si>
+  <si>
+    <t>cake</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -367,8 +404,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="20.77734375" customWidth="1"/>
@@ -385,6 +422,94 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
